--- a/python/assets/批量引文模板.xlsx
+++ b/python/assets/批量引文模板.xlsx
@@ -1,57 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3654B13-47F2-4F5E-A7CE-AE81F421E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="论文列表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>序号</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="0"/>
   </si>
   <si>
     <t>标题</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="0"/>
   </si>
   <si>
     <t>引文</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="0"/>
   </si>
   <si>
     <t>新形势下企业财务管理信息化建设的途径探索</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>柯玲巧.新形势下企业财务管理信息化建设的途径探索[J].活力,2024,42(17):40-42.</t>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="0"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="&amp;#x5B8B;&amp;#x4F53;"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,16 +78,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -362,9 +376,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
@@ -377,19 +391,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" ht="16.5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
+  <phoneticPr fontId="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/python/assets/批量引文模板.xlsx
+++ b/python/assets/批量引文模板.xlsx
@@ -1,52 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3654B13-47F2-4F5E-A7CE-AE81F421E025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="论文列表" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="9">
   <si>
     <t>序号</t>
-    <phoneticPr fontId="0"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>标题</t>
-    <phoneticPr fontId="0"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>引文</t>
-    <phoneticPr fontId="0"/>
+    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>新形势下企业财务管理信息化建设的途径探索</t>
-    <phoneticPr fontId="0"/>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>序号</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>标题</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>引文</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>新形势下企业财务管理信息化建设的途径探索</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>柯玲巧.新形势下企业财务管理信息化建设的途径探索[J].活力,2024,42(17):40-42.</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="&amp;#x5B8B;&amp;#x4F53;"/>
+      <name val="&amp;amp;#x5B8B;&amp;amp;#x4F53;"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -85,14 +99,10 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -144,10 +154,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="&amp;#xFF2D;&amp;#xFF33; &amp;#xFF30;&amp;#x30B4;&amp;#x30B7;&amp;#x30C3;&amp;#x30AF;"/>
-        <a:font script="Hang" typeface="&amp;#xB9D1;&amp;#xC740; &amp;#xACE0;&amp;#xB515;"/>
-        <a:font script="Hans" typeface="&amp;#x5B8B;&amp;#x4F53;"/>
-        <a:font script="Hant" typeface="&amp;#x65B0;&amp;#x7D30;&amp;#x660E;&amp;#x9AD4;"/>
+        <a:font script="Jpan" typeface="&amp;amp;#xFF2D;&amp;amp;#xFF33; &amp;amp;#xFF30;&amp;amp;#x30B4;&amp;amp;#x30B7;&amp;amp;#x30C3;&amp;amp;#x30AF;"/>
+        <a:font script="Hang" typeface="&amp;amp;#xB9D1;&amp;amp;#xC740; &amp;amp;#xACE0;&amp;amp;#xB515;"/>
+        <a:font script="Hans" typeface="&amp;amp;#x5B8B;&amp;amp;#x4F53;"/>
+        <a:font script="Hant" typeface="&amp;amp;#x65B0;&amp;amp;#x7D30;&amp;amp;#x660E;&amp;amp;#x9AD4;"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -178,10 +188,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="&amp;#xFF2D;&amp;#xFF33; &amp;#xFF30;&amp;#x30B4;&amp;#x30B7;&amp;#x30C3;&amp;#x30AF;"/>
-        <a:font script="Hang" typeface="&amp;#xB9D1;&amp;#xC740; &amp;#xACE0;&amp;#xB515;"/>
-        <a:font script="Hans" typeface="&amp;#x5B8B;&amp;#x4F53;"/>
-        <a:font script="Hant" typeface="&amp;#x65B0;&amp;#x7D30;&amp;#x660E;&amp;#x9AD4;"/>
+        <a:font script="Jpan" typeface="&amp;amp;#xFF2D;&amp;amp;#xFF33; &amp;amp;#xFF30;&amp;amp;#x30B4;&amp;amp;#x30B7;&amp;amp;#x30C3;&amp;amp;#x30AF;"/>
+        <a:font script="Hang" typeface="&amp;amp;#xB9D1;&amp;amp;#xC740; &amp;amp;#xACE0;&amp;amp;#xB515;"/>
+        <a:font script="Hans" typeface="&amp;amp;#x5B8B;&amp;amp;#x4F53;"/>
+        <a:font script="Hant" typeface="&amp;amp;#x65B0;&amp;amp;#x7D30;&amp;amp;#x660E;&amp;amp;#x9AD4;"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -376,31 +386,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="16.5">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>3</v>
+      <c r="B2" t="s" s="1">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="0"/>
+  <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>